--- a/data/output/2025/evaluasi_73.xlsx
+++ b/data/output/2025/evaluasi_73.xlsx
@@ -1979,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,6 +2263,370 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.367473742788764</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.690864387551787</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-6.437295124584103</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.81474542883618</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8.918886490495435</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-5.333863473484571</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.67657498296504</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6.613295627406124</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6897103601099852</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.057666660228521</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.471140954949924</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5.686043651435917</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2449,6 +2813,342 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.697144288904849</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.69447253705318</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>32.06212778593465</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-15.25759876187242</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-4.620000381463474</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.232579751933786</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-7.601350854326215</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-5.113097890914133</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.045218194441889</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.8737095886381764</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.300653305298404</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2463,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2971,6 +3671,258 @@
       <c r="F18" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3.71141420395738</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9.763701369533972</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>44.63024983313723</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.25739005750566</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.383649097645585</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2.064749420132565</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.9140417538403233</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.875326270809994</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3255,18 +4207,298 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>3.201391239151224</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.365074231768644</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>25.80000053973991</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.714048599266171</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-10.77181970937806</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.7060952312177866</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2090234034724801</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.5013073193904063</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.288078548619544</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>3.054134145932453</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3283,7 +4515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,18 +4841,326 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>5.677057899145177</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6.870176752066914</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>18.09392070164943</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-10.83882631291726</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-5.001507537718788</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-6.053287927958731</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.09506406476086088</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.399808443623459</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4.929478425966886</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.547640844436611</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>4.229450867226128</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3637,7 +5177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +5377,230 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.168616017137284</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9.655092712087248</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>32.09000124533473</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-8.098515865033464</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-3.562441665387251</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.363429988976837</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9391301147299299</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3851,7 +5615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4233,20 +5997,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.406350990735564</v>
+        <v>4.642294309207442</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4261,18 +6025,382 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>14.99995563324667</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>60.9999920632751</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>19.51642827218863</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-34.12288042670797</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-16.55607541717358</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.04056858867211</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6621222666725631</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8.69565753222067</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3.883381943696477</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6.443738402158028</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5.644150963080995</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6.406350990735564</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>-5.144079011428184</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4289,7 +6417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4405,6 +6533,314 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.027381027248734</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.807057297075508</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>21.41617055605523</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.832088364113233</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.01691382932664848</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.05896226587356257</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.008116305383067424</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.074780443186131</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.171438296177399</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7306</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Gowa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.811670111372991</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4419,7 +6855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4535,6 +6971,258 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.044326031837923</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3273355220394054</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>62.62845808098925</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.56926911314985</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-7.915299963797402</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-4.297906319329278</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.085478962131295</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.27649575558106</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4549,7 +7237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4777,6 +7465,286 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8.037198728946379</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.3915738666354</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.564853331750232</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>22.29239478121554</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.04646818736901717</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.909963396047566</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.027448958736885</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.3225949554172461</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.147540043857404</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4791,7 +7759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5019,6 +7987,342 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.780156269360746</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.444902332075311</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>19.6221488733899</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.208001849306707</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2489930797011273</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.362280753644441</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.781581680531097</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1482352470332103</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.149760450116682</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.945145291014184</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5.55203266340633</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5033,7 +8337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5121,6 +8425,258 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7313</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Wajo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.145250290916818</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7313</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Wajo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.072233477175638</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7313</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Wajo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>22.92204639462566</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7313</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Wajo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7313</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Wajo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-9.140001772027135</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7313</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Wajo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.613157077667774</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7313</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Wajo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8506227301688967</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7313</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Wajo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.818859644583771</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7313</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Wajo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.857032230473041</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5135,7 +8691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5195,6 +8751,314 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.237698923242057</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.797418967423445</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.960000000000047</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16.84000000000306</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3861857157938637</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.52707799633482</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.162025830469583</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1589350027627184</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4100000000010057</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.99434863125634</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5209,7 +9073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5269,6 +9133,314 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.03982597964257</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.90508247614126</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.198809135067744</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>20.97715849094291</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5838704222419844</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.414419835900107</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.146455820864069</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1326411253513999</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.5128660080847175</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.993352735314903</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5283,7 +9455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5371,6 +9543,230 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.456918969905829</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.681040908242338</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>22.96888602701602</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-10.61395203120244</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.6731128903526392</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-3.569150493889447</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.4075141613077</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5385,7 +9781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5445,6 +9841,286 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.671485714039982</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.239975742307131</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>30.96811064093765</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-11.65564972727575</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-4.300589482119761</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-7.006496842076118</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.742895538562187</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.584551855721756</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.338913729250908</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5459,7 +10135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5603,6 +10279,314 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-11.23792351699905</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.82343918809567</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-6.724641466656325</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-8.730888011810285</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-7.914747342636222</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>20.61452045442183</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-7.45352829337668</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.119828954323896</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4.179241379557115</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7.338043124390414</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5617,7 +10601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5733,6 +10717,286 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.07284026886605</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.917801338277505</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.134719827104787</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>19.03023686622329</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.3656589759073609</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.167535241108999</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8441206537447439</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1823092035222322</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7214628128053839</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5747,7 +11011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5919,6 +11183,370 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.179975939747958</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.35797128300021</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.550000000001783</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>19.56906511583033</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.02737033995286107</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.501269399713702</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4365427674010438</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.045659235979563</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-2.384365619771361</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.923084061000274</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.975186918607217</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6.22568548268854</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5933,7 +11561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6245,6 +11873,286 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.875667305584231</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.18513201058477</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16.14590994019056</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.562329877957058</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.008769158354628562</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.06454119381817</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.490586445761905</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.2151272857573828</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2.224927728400142</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -6259,7 +12167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6487,6 +12395,314 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.175448783299096</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9.56870181883615</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.904635367223332</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>22.92349397892924</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1583780370268065</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.934961436679951</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.008821826617691</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.02956903920511499</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2978937871674259</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.867911367909982</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -6501,7 +12717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6673,6 +12889,258 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.602924036679042</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.91031847700777</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>27.56751999721134</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.02572285287861125</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3205946086882854</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8484588119808025</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.2611612269705444</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.770572484200059</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -6687,7 +13155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6859,6 +13327,286 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.489382731288376</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8.780826223151792</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.987480181067969</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>19.72368786722295</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.694679979242064</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.038685995862985</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8150525364793717</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.216291797383825</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.044604719155418</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -6873,7 +13621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7244,6 +13992,258 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.556506260675163</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8.003891033609541</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1520671581762733</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-8.800378358470788</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-4.387088181668744</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-5.782935007407036</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5273997055572333</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.747716337543853</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
